--- a/downloads/inventario-acquisto-banco.xlsx
+++ b/downloads/inventario-acquisto-banco.xlsx
@@ -507,7 +507,7 @@
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Non inserire nomi o descrizioni nella colonna dei codici numerici.</t>
+          <t>Quantit?: inserisci pezzi interi. Per i valori unitari puoi usare i decimali.</t>
         </is>
       </c>
     </row>
